--- a/robust_data/sample/Validasi_Manual_356_Proporsional.xlsx
+++ b/robust_data/sample/Validasi_Manual_356_Proporsional.xlsx
@@ -8,15 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tokped-scraper\robust_data\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A18F4109-6794-43D2-9549-08526CC5173C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA53B6B6-C8EF-41FE-B6F4-E3441E82EBAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Validasi_356" sheetId="1" r:id="rId1"/>
+    <sheet name="ACC" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -25,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2145" uniqueCount="990">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2453" uniqueCount="999">
   <si>
     <t>Username</t>
   </si>
@@ -2040,10 +2050,6 @@
     <t>chat ke penjual yang jawab mesin terus, penjual kurang ramah, saya minta faktur pajak aja susah. harus minta di awal pembelianlah, di toko lain bisa kok walau SDH transak...</t>
   </si>
   <si>
-    <t>anti gores sedikit miring, cleaning kit tidak ada. cover belakang bikin jadi body _x000D_
-keliatan jelek alhasil gadipakai. tp pelayanan ok ,hanya saja barang menurut saya kuran...</t>
-  </si>
-  <si>
     <t>1 unit charger laptop tidak sesuai.</t>
   </si>
   <si>
@@ -3101,12 +3107,44 @@
   <si>
     <t>(label benar)/(total sampel)x100%</t>
   </si>
+  <si>
+    <t>Keterangan</t>
+  </si>
+  <si>
+    <t>Validasi (v) (x)</t>
+  </si>
+  <si>
+    <t>Label (Sistem)</t>
+  </si>
+  <si>
+    <t>Label (Manual)</t>
+  </si>
+  <si>
+    <t>Ulasan</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>anti gores sedikit miring, cleaning kit tidak ada. cover belakang bikin jadi body 
+keliatan jelek alhasil gadipakai. tp pelayanan ok ,hanya saja barang menurut saya kuran...</t>
+  </si>
+  <si>
+    <t>anti gores sedikit miring, cleaning kit tidak ada. cover belakang bikin jadi body 
+keliatan jelek alhasil gadipakai. tp pelayanan ok ,hanya saja barang menurut saya kuran…</t>
+  </si>
+  <si>
+    <t>Nganjuk, 20-04-2026</t>
+  </si>
+  <si>
+    <t>Ttd, Nama terang</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3125,6 +3163,12 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3198,7 +3242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -3211,6 +3255,24 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3551,7 +3613,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G360"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.65" thickBottom="1" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="15.73046875" customWidth="1"/>
     <col min="2" max="3" width="10.73046875" customWidth="1"/>
@@ -3560,7 +3622,7 @@
     <col min="7" max="7" width="15.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3583,7 +3645,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -3594,19 +3656,19 @@
         <v>307</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>310</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="G2" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -3623,13 +3685,13 @@
         <v>311</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="G3" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3640,19 +3702,19 @@
         <v>307</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>312</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G4" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -3663,19 +3725,19 @@
         <v>307</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>313</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G5" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -3686,19 +3748,19 @@
         <v>307</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>314</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G6" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="52.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3709,19 +3771,19 @@
         <v>307</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>315</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="G7" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -3732,19 +3794,19 @@
         <v>307</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>316</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="G8" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -3755,19 +3817,19 @@
         <v>307</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>317</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="G9" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -3778,19 +3840,19 @@
         <v>307</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>318</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G10" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -3801,19 +3863,19 @@
         <v>307</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>319</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G11" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -3824,19 +3886,19 @@
         <v>307</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>320</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G12" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -3847,19 +3909,19 @@
         <v>307</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>321</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G13" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -3870,19 +3932,19 @@
         <v>307</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>322</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G14" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -3893,19 +3955,19 @@
         <v>307</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>323</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G15" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -3916,19 +3978,19 @@
         <v>307</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>324</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G16" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -3939,19 +4001,19 @@
         <v>307</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>325</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G17" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -3962,19 +4024,19 @@
         <v>307</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>326</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G18" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -3985,19 +4047,19 @@
         <v>307</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>327</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="G19" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -4008,19 +4070,19 @@
         <v>307</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>328</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G20" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -4031,19 +4093,19 @@
         <v>307</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>329</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G21" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -4054,19 +4116,19 @@
         <v>307</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>330</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G22" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -4077,19 +4139,19 @@
         <v>307</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>331</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G23" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="52.5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:7" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -4100,19 +4162,19 @@
         <v>307</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>332</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="G24" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -4123,19 +4185,19 @@
         <v>307</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>333</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G25" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="52.5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:7" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -4146,19 +4208,19 @@
         <v>307</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>334</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G26" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -4169,19 +4231,19 @@
         <v>307</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>335</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G27" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -4192,19 +4254,19 @@
         <v>307</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>336</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G28" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -4215,19 +4277,19 @@
         <v>307</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>337</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="G29" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="65.650000000000006" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -4238,19 +4300,19 @@
         <v>307</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>338</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="G30" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -4261,19 +4323,19 @@
         <v>307</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>339</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="G31" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A32" t="s">
         <v>36</v>
       </c>
@@ -4284,19 +4346,19 @@
         <v>307</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>340</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="G32" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A33" t="s">
         <v>37</v>
       </c>
@@ -4307,19 +4369,19 @@
         <v>307</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>341</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="G33" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -4330,19 +4392,19 @@
         <v>307</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>342</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="G34" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -4353,19 +4415,19 @@
         <v>307</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>343</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="G35" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -4376,19 +4438,19 @@
         <v>307</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>344</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="G36" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -4399,19 +4461,19 @@
         <v>307</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>345</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G37" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -4422,19 +4484,19 @@
         <v>307</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>346</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="G38" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -4445,19 +4507,19 @@
         <v>307</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>347</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="G39" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -4468,19 +4530,19 @@
         <v>307</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>348</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="G40" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -4491,19 +4553,19 @@
         <v>307</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>349</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="G41" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -4514,19 +4576,19 @@
         <v>307</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>350</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="G42" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A43" t="s">
         <v>13</v>
       </c>
@@ -4537,19 +4599,19 @@
         <v>307</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>351</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="G43" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="78.75" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:7" ht="79.150000000000006" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A44" t="s">
         <v>47</v>
       </c>
@@ -4560,19 +4622,19 @@
         <v>307</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>352</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="G44" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A45" t="s">
         <v>48</v>
       </c>
@@ -4583,19 +4645,19 @@
         <v>307</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>353</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="G45" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A46" t="s">
         <v>49</v>
       </c>
@@ -4606,19 +4668,19 @@
         <v>307</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>354</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="G46" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A47" t="s">
         <v>50</v>
       </c>
@@ -4629,7 +4691,7 @@
         <v>307</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>355</v>
@@ -4641,7 +4703,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A48" t="s">
         <v>51</v>
       </c>
@@ -4652,19 +4714,19 @@
         <v>307</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>356</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="G48" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A49" t="s">
         <v>52</v>
       </c>
@@ -4675,19 +4737,19 @@
         <v>307</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>357</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="G49" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A50" t="s">
         <v>53</v>
       </c>
@@ -4698,19 +4760,19 @@
         <v>307</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>358</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="G50" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A51" t="s">
         <v>54</v>
       </c>
@@ -4721,19 +4783,19 @@
         <v>307</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>359</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="G51" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A52" t="s">
         <v>13</v>
       </c>
@@ -4744,19 +4806,19 @@
         <v>307</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>360</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="G52" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A53" t="s">
         <v>55</v>
       </c>
@@ -4767,19 +4829,19 @@
         <v>307</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>361</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="G53" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A54" t="s">
         <v>56</v>
       </c>
@@ -4790,19 +4852,19 @@
         <v>307</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>362</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="G54" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A55" t="s">
         <v>57</v>
       </c>
@@ -4813,19 +4875,19 @@
         <v>307</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>363</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="G55" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A56" t="s">
         <v>58</v>
       </c>
@@ -4836,19 +4898,19 @@
         <v>307</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>364</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="G56" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A57" t="s">
         <v>59</v>
       </c>
@@ -4859,19 +4921,19 @@
         <v>307</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>365</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="G57" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A58" t="s">
         <v>60</v>
       </c>
@@ -4882,19 +4944,19 @@
         <v>307</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>366</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="G58" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A59" t="s">
         <v>61</v>
       </c>
@@ -4905,19 +4967,19 @@
         <v>307</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>367</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="G59" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="52.5" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:7" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A60" t="s">
         <v>62</v>
       </c>
@@ -4928,19 +4990,19 @@
         <v>307</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>368</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="G60" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A61" t="s">
         <v>63</v>
       </c>
@@ -4951,19 +5013,19 @@
         <v>307</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>369</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="G61" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A62" t="s">
         <v>64</v>
       </c>
@@ -4974,19 +5036,19 @@
         <v>307</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>370</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="G62" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A63" t="s">
         <v>65</v>
       </c>
@@ -4997,19 +5059,19 @@
         <v>307</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>371</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="G63" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A64" t="s">
         <v>66</v>
       </c>
@@ -5020,19 +5082,19 @@
         <v>307</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>372</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="G64" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A65" t="s">
         <v>67</v>
       </c>
@@ -5043,19 +5105,19 @@
         <v>307</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>373</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="G65" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A66" t="s">
         <v>68</v>
       </c>
@@ -5066,19 +5128,19 @@
         <v>307</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>374</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="G66" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A67" t="s">
         <v>31</v>
       </c>
@@ -5089,19 +5151,19 @@
         <v>307</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>375</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="G67" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A68" t="s">
         <v>69</v>
       </c>
@@ -5112,19 +5174,19 @@
         <v>307</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>376</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="G68" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A69" t="s">
         <v>70</v>
       </c>
@@ -5135,19 +5197,19 @@
         <v>307</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>377</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="G69" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A70" t="s">
         <v>71</v>
       </c>
@@ -5158,19 +5220,19 @@
         <v>307</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>378</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="G70" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A71" t="s">
         <v>72</v>
       </c>
@@ -5181,19 +5243,19 @@
         <v>307</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>379</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="G71" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A72" t="s">
         <v>73</v>
       </c>
@@ -5204,19 +5266,19 @@
         <v>307</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>380</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="G72" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A73" t="s">
         <v>13</v>
       </c>
@@ -5227,19 +5289,19 @@
         <v>307</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>381</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="G73" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A74" t="s">
         <v>64</v>
       </c>
@@ -5250,19 +5312,19 @@
         <v>307</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>382</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="G74" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A75" t="s">
         <v>74</v>
       </c>
@@ -5273,19 +5335,19 @@
         <v>307</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>383</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="G75" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A76" t="s">
         <v>75</v>
       </c>
@@ -5296,19 +5358,19 @@
         <v>307</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>384</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="G76" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A77" t="s">
         <v>76</v>
       </c>
@@ -5319,19 +5381,19 @@
         <v>307</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>385</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="G77" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A78" t="s">
         <v>77</v>
       </c>
@@ -5342,19 +5404,19 @@
         <v>307</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>386</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="G78" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A79" t="s">
         <v>78</v>
       </c>
@@ -5365,19 +5427,19 @@
         <v>307</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>387</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="G79" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A80" t="s">
         <v>79</v>
       </c>
@@ -5388,7 +5450,7 @@
         <v>307</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>388</v>
@@ -5400,7 +5462,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="52.5" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:7" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A81" t="s">
         <v>80</v>
       </c>
@@ -5411,19 +5473,19 @@
         <v>307</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>389</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="G81" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A82" t="s">
         <v>81</v>
       </c>
@@ -5434,19 +5496,19 @@
         <v>307</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>390</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="G82" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A83" t="s">
         <v>82</v>
       </c>
@@ -5457,19 +5519,19 @@
         <v>307</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>391</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="G83" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A84" t="s">
         <v>83</v>
       </c>
@@ -5480,19 +5542,19 @@
         <v>307</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>392</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="G84" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A85" t="s">
         <v>84</v>
       </c>
@@ -5503,19 +5565,19 @@
         <v>307</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>393</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="G85" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A86" t="s">
         <v>85</v>
       </c>
@@ -5526,19 +5588,19 @@
         <v>307</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>394</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G86" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A87" t="s">
         <v>86</v>
       </c>
@@ -5549,7 +5611,7 @@
         <v>307</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>395</v>
@@ -5561,7 +5623,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A88" t="s">
         <v>87</v>
       </c>
@@ -5572,19 +5634,19 @@
         <v>307</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>396</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="G88" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A89" t="s">
         <v>88</v>
       </c>
@@ -5595,19 +5657,19 @@
         <v>307</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>397</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="G89" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A90" t="s">
         <v>89</v>
       </c>
@@ -5618,19 +5680,19 @@
         <v>307</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>398</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="G90" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A91" t="s">
         <v>90</v>
       </c>
@@ -5641,19 +5703,19 @@
         <v>307</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>399</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="G91" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A92" t="s">
         <v>91</v>
       </c>
@@ -5664,19 +5726,19 @@
         <v>307</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>400</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="G92" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A93" t="s">
         <v>92</v>
       </c>
@@ -5687,19 +5749,19 @@
         <v>307</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>401</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="G93" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A94" t="s">
         <v>93</v>
       </c>
@@ -5710,19 +5772,19 @@
         <v>307</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>402</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="G94" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A95" t="s">
         <v>94</v>
       </c>
@@ -5733,19 +5795,19 @@
         <v>307</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>403</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="G95" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A96" t="s">
         <v>95</v>
       </c>
@@ -5756,19 +5818,19 @@
         <v>307</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>404</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="G96" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A97" t="s">
         <v>96</v>
       </c>
@@ -5779,19 +5841,19 @@
         <v>307</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>405</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="G97" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A98" t="s">
         <v>97</v>
       </c>
@@ -5802,19 +5864,19 @@
         <v>307</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>406</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="G98" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A99" t="s">
         <v>13</v>
       </c>
@@ -5825,19 +5887,19 @@
         <v>307</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>407</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="G99" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="52.5" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:7" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A100" t="s">
         <v>98</v>
       </c>
@@ -5848,19 +5910,19 @@
         <v>307</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>408</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="G100" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A101" t="s">
         <v>99</v>
       </c>
@@ -5871,19 +5933,19 @@
         <v>307</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>409</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="G101" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A102" t="s">
         <v>100</v>
       </c>
@@ -5900,13 +5962,13 @@
         <v>410</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G102" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A103" t="s">
         <v>101</v>
       </c>
@@ -5917,19 +5979,19 @@
         <v>307</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>411</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="G103" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A104" t="s">
         <v>31</v>
       </c>
@@ -5940,19 +6002,19 @@
         <v>307</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>412</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="G104" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A105" t="s">
         <v>102</v>
       </c>
@@ -5963,19 +6025,19 @@
         <v>307</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>413</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="G105" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A106" t="s">
         <v>103</v>
       </c>
@@ -5986,19 +6048,19 @@
         <v>307</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>414</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="G106" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A107" t="s">
         <v>104</v>
       </c>
@@ -6009,19 +6071,19 @@
         <v>307</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>415</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="G107" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A108" t="s">
         <v>59</v>
       </c>
@@ -6032,19 +6094,19 @@
         <v>307</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>416</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="G108" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A109" t="s">
         <v>105</v>
       </c>
@@ -6055,19 +6117,19 @@
         <v>307</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>417</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G109" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A110" t="s">
         <v>106</v>
       </c>
@@ -6078,19 +6140,19 @@
         <v>307</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>418</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="G110" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A111" t="s">
         <v>107</v>
       </c>
@@ -6101,19 +6163,19 @@
         <v>307</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>419</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="G111" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A112" t="s">
         <v>108</v>
       </c>
@@ -6124,19 +6186,19 @@
         <v>307</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>420</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="G112" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A113" t="s">
         <v>109</v>
       </c>
@@ -6147,19 +6209,19 @@
         <v>307</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>421</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="G113" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A114" t="s">
         <v>110</v>
       </c>
@@ -6170,19 +6232,19 @@
         <v>307</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>422</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="G114" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="52.5" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:7" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A115" t="s">
         <v>13</v>
       </c>
@@ -6193,19 +6255,19 @@
         <v>307</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>423</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="G115" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A116" t="s">
         <v>111</v>
       </c>
@@ -6216,19 +6278,19 @@
         <v>307</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>424</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="G116" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A117" t="s">
         <v>112</v>
       </c>
@@ -6239,19 +6301,19 @@
         <v>307</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>425</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G117" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A118" t="s">
         <v>113</v>
       </c>
@@ -6262,19 +6324,19 @@
         <v>307</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>426</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="G118" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A119" t="s">
         <v>114</v>
       </c>
@@ -6285,19 +6347,19 @@
         <v>307</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>427</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="G119" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A120" t="s">
         <v>115</v>
       </c>
@@ -6308,19 +6370,19 @@
         <v>307</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>428</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G120" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A121" t="s">
         <v>101</v>
       </c>
@@ -6331,19 +6393,19 @@
         <v>307</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>429</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="G121" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A122" t="s">
         <v>116</v>
       </c>
@@ -6354,19 +6416,19 @@
         <v>307</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>430</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="G122" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A123" t="s">
         <v>117</v>
       </c>
@@ -6377,19 +6439,19 @@
         <v>307</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>431</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="G123" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A124" t="s">
         <v>118</v>
       </c>
@@ -6400,19 +6462,19 @@
         <v>307</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>432</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="G124" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A125" t="s">
         <v>119</v>
       </c>
@@ -6423,19 +6485,19 @@
         <v>307</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>433</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="G125" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A126" t="s">
         <v>120</v>
       </c>
@@ -6446,19 +6508,19 @@
         <v>307</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>434</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="G126" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A127" t="s">
         <v>121</v>
       </c>
@@ -6469,19 +6531,19 @@
         <v>307</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>435</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="G127" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A128" t="s">
         <v>122</v>
       </c>
@@ -6492,19 +6554,19 @@
         <v>307</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>436</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="G128" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.45">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A129" t="s">
         <v>123</v>
       </c>
@@ -6515,19 +6577,19 @@
         <v>307</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>437</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="G129" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A130" t="s">
         <v>30</v>
       </c>
@@ -6538,19 +6600,19 @@
         <v>307</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>438</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="G130" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A131" t="s">
         <v>124</v>
       </c>
@@ -6561,19 +6623,19 @@
         <v>307</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>439</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="G131" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A132" t="s">
         <v>45</v>
       </c>
@@ -6584,19 +6646,19 @@
         <v>307</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>440</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="G132" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A133" t="s">
         <v>125</v>
       </c>
@@ -6607,19 +6669,19 @@
         <v>307</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>441</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="G133" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A134" t="s">
         <v>126</v>
       </c>
@@ -6630,19 +6692,19 @@
         <v>307</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>442</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="G134" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A135" t="s">
         <v>127</v>
       </c>
@@ -6653,19 +6715,19 @@
         <v>307</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>443</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="G135" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A136" t="s">
         <v>128</v>
       </c>
@@ -6676,19 +6738,19 @@
         <v>307</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>444</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="G136" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A137" t="s">
         <v>129</v>
       </c>
@@ -6699,19 +6761,19 @@
         <v>307</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>445</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="G137" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="52.5" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:7" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A138" t="s">
         <v>130</v>
       </c>
@@ -6722,19 +6784,19 @@
         <v>307</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>446</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G138" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A139" t="s">
         <v>131</v>
       </c>
@@ -6745,19 +6807,19 @@
         <v>307</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>447</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="G139" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A140" t="s">
         <v>132</v>
       </c>
@@ -6768,19 +6830,19 @@
         <v>307</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>448</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="G140" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A141" t="s">
         <v>133</v>
       </c>
@@ -6791,7 +6853,7 @@
         <v>307</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>449</v>
@@ -6803,7 +6865,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A142" t="s">
         <v>134</v>
       </c>
@@ -6814,19 +6876,19 @@
         <v>307</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>450</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="G142" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A143" t="s">
         <v>135</v>
       </c>
@@ -6837,19 +6899,19 @@
         <v>307</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>451</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="G143" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A144" t="s">
         <v>136</v>
       </c>
@@ -6860,19 +6922,19 @@
         <v>307</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>452</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="G144" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A145" t="s">
         <v>137</v>
       </c>
@@ -6883,19 +6945,19 @@
         <v>307</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>453</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="G145" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A146" t="s">
         <v>138</v>
       </c>
@@ -6906,19 +6968,19 @@
         <v>307</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>454</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="G146" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A147" t="s">
         <v>139</v>
       </c>
@@ -6929,19 +6991,19 @@
         <v>307</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>455</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="G147" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A148" t="s">
         <v>140</v>
       </c>
@@ -6952,19 +7014,19 @@
         <v>307</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>456</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="G148" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A149" t="s">
         <v>141</v>
       </c>
@@ -6975,19 +7037,19 @@
         <v>307</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>457</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="G149" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A150" t="s">
         <v>142</v>
       </c>
@@ -6998,19 +7060,19 @@
         <v>307</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>458</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="G150" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A151" t="s">
         <v>143</v>
       </c>
@@ -7021,19 +7083,19 @@
         <v>307</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>459</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="G151" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A152" t="s">
         <v>144</v>
       </c>
@@ -7044,19 +7106,19 @@
         <v>307</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>460</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="G152" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A153" t="s">
         <v>145</v>
       </c>
@@ -7067,19 +7129,19 @@
         <v>307</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>461</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="G153" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="154" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A154" t="s">
         <v>146</v>
       </c>
@@ -7090,19 +7152,19 @@
         <v>307</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>462</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="G154" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A155" t="s">
         <v>147</v>
       </c>
@@ -7113,19 +7175,19 @@
         <v>307</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>463</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="G155" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A156" t="s">
         <v>148</v>
       </c>
@@ -7136,19 +7198,19 @@
         <v>307</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>464</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="G156" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A157" t="s">
         <v>149</v>
       </c>
@@ -7159,19 +7221,19 @@
         <v>307</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>465</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="G157" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A158" t="s">
         <v>150</v>
       </c>
@@ -7182,19 +7244,19 @@
         <v>307</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>466</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="G158" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="159" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A159" t="s">
         <v>61</v>
       </c>
@@ -7205,19 +7267,19 @@
         <v>307</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>467</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="G159" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="160" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A160" t="s">
         <v>151</v>
       </c>
@@ -7228,19 +7290,19 @@
         <v>307</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>468</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="G160" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A161" t="s">
         <v>152</v>
       </c>
@@ -7251,19 +7313,19 @@
         <v>307</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>469</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="G161" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A162" t="s">
         <v>153</v>
       </c>
@@ -7274,19 +7336,19 @@
         <v>307</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>470</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="G162" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A163" t="s">
         <v>154</v>
       </c>
@@ -7297,19 +7359,19 @@
         <v>307</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>471</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G163" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A164" t="s">
         <v>155</v>
       </c>
@@ -7320,19 +7382,19 @@
         <v>307</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>472</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="G164" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A165" t="s">
         <v>156</v>
       </c>
@@ -7343,19 +7405,19 @@
         <v>307</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>473</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G165" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A166" t="s">
         <v>157</v>
       </c>
@@ -7366,19 +7428,19 @@
         <v>307</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>474</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="G166" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A167" t="s">
         <v>158</v>
       </c>
@@ -7389,19 +7451,19 @@
         <v>307</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>475</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="G167" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="168" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A168" t="s">
         <v>159</v>
       </c>
@@ -7412,19 +7474,19 @@
         <v>307</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>476</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="G168" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="169" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A169" t="s">
         <v>160</v>
       </c>
@@ -7435,19 +7497,19 @@
         <v>307</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>477</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="G169" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A170" t="s">
         <v>161</v>
       </c>
@@ -7458,19 +7520,19 @@
         <v>307</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>478</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="G170" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A171" t="s">
         <v>162</v>
       </c>
@@ -7481,19 +7543,19 @@
         <v>307</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>479</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="G171" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A172" t="s">
         <v>163</v>
       </c>
@@ -7504,19 +7566,19 @@
         <v>307</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>480</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="G172" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="173" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A173" t="s">
         <v>164</v>
       </c>
@@ -7527,19 +7589,19 @@
         <v>307</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>481</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="G173" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.45">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A174" t="s">
         <v>165</v>
       </c>
@@ -7550,19 +7612,19 @@
         <v>307</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>482</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="G174" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A175" t="s">
         <v>16</v>
       </c>
@@ -7573,19 +7635,19 @@
         <v>307</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>483</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="G175" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A176" t="s">
         <v>166</v>
       </c>
@@ -7596,19 +7658,19 @@
         <v>307</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>484</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="G176" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A177" t="s">
         <v>167</v>
       </c>
@@ -7619,19 +7681,19 @@
         <v>307</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>485</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="G177" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="52.5" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:7" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A178" t="s">
         <v>168</v>
       </c>
@@ -7642,19 +7704,19 @@
         <v>307</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>486</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="G178" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A179" t="s">
         <v>169</v>
       </c>
@@ -7665,19 +7727,19 @@
         <v>307</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>487</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="G179" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A180" t="s">
         <v>170</v>
       </c>
@@ -7694,13 +7756,13 @@
         <v>488</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="G180" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.45">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A181" t="s">
         <v>81</v>
       </c>
@@ -7711,19 +7773,19 @@
         <v>308</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>489</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="G181" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A182" t="s">
         <v>38</v>
       </c>
@@ -7734,19 +7796,19 @@
         <v>308</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>490</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="G182" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="183" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A183" t="s">
         <v>171</v>
       </c>
@@ -7757,19 +7819,19 @@
         <v>308</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>491</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="G183" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A184" t="s">
         <v>172</v>
       </c>
@@ -7780,19 +7842,19 @@
         <v>308</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>492</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="G184" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A185" t="s">
         <v>173</v>
       </c>
@@ -7803,19 +7865,19 @@
         <v>308</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>493</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="G185" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="186" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A186" t="s">
         <v>174</v>
       </c>
@@ -7826,19 +7888,19 @@
         <v>308</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>494</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="G186" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A187" t="s">
         <v>175</v>
       </c>
@@ -7849,19 +7911,19 @@
         <v>308</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>495</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G187" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" ht="52.5" x14ac:dyDescent="0.45">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A188" t="s">
         <v>176</v>
       </c>
@@ -7878,13 +7940,13 @@
         <v>496</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="G188" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="189" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A189" t="s">
         <v>177</v>
       </c>
@@ -7895,19 +7957,19 @@
         <v>308</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>497</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="G189" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A190" t="s">
         <v>178</v>
       </c>
@@ -7918,7 +7980,7 @@
         <v>308</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>498</v>
@@ -7930,7 +7992,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="191" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A191" t="s">
         <v>179</v>
       </c>
@@ -7941,19 +8003,19 @@
         <v>308</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>499</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="G191" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="192" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A192" t="s">
         <v>180</v>
       </c>
@@ -7964,19 +8026,19 @@
         <v>308</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>500</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G192" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A193" t="s">
         <v>181</v>
       </c>
@@ -7993,13 +8055,13 @@
         <v>410</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="G193" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="194" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A194" t="s">
         <v>182</v>
       </c>
@@ -8010,19 +8072,19 @@
         <v>308</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>501</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="G194" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A195" t="s">
         <v>183</v>
       </c>
@@ -8039,13 +8101,13 @@
         <v>502</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="G195" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A196" t="s">
         <v>184</v>
       </c>
@@ -8056,19 +8118,19 @@
         <v>308</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>503</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="G196" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="197" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A197" t="s">
         <v>185</v>
       </c>
@@ -8079,19 +8141,19 @@
         <v>308</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>504</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="G197" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A198" t="s">
         <v>186</v>
       </c>
@@ -8108,13 +8170,13 @@
         <v>505</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="G198" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A199" t="s">
         <v>187</v>
       </c>
@@ -8131,13 +8193,13 @@
         <v>506</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="G199" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A200" t="s">
         <v>188</v>
       </c>
@@ -8148,19 +8210,19 @@
         <v>308</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>507</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="G200" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="201" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A201" t="s">
         <v>189</v>
       </c>
@@ -8171,19 +8233,19 @@
         <v>308</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>508</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="G201" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A202" t="s">
         <v>30</v>
       </c>
@@ -8194,19 +8256,19 @@
         <v>308</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>509</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="G202" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A203" t="s">
         <v>190</v>
       </c>
@@ -8223,13 +8285,13 @@
         <v>510</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="G203" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A204" t="s">
         <v>31</v>
       </c>
@@ -8240,19 +8302,19 @@
         <v>308</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>511</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="G204" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A205" t="s">
         <v>191</v>
       </c>
@@ -8263,19 +8325,19 @@
         <v>308</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>512</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="G205" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A206" t="s">
         <v>178</v>
       </c>
@@ -8286,19 +8348,19 @@
         <v>308</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>513</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="G206" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="207" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A207" t="s">
         <v>192</v>
       </c>
@@ -8309,19 +8371,19 @@
         <v>308</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>514</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="G207" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7" ht="52.5" x14ac:dyDescent="0.45">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A208" t="s">
         <v>193</v>
       </c>
@@ -8332,19 +8394,19 @@
         <v>308</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>515</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="G208" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A209" t="s">
         <v>194</v>
       </c>
@@ -8355,19 +8417,19 @@
         <v>308</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>516</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="G209" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A210" t="s">
         <v>195</v>
       </c>
@@ -8378,19 +8440,19 @@
         <v>308</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>517</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="G210" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="211" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A211" t="s">
         <v>196</v>
       </c>
@@ -8401,19 +8463,19 @@
         <v>308</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>518</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="G211" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="212" spans="1:7" ht="52.5" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:7" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A212" t="s">
         <v>197</v>
       </c>
@@ -8424,19 +8486,19 @@
         <v>308</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>519</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="G212" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="213" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A213" t="s">
         <v>198</v>
       </c>
@@ -8447,19 +8509,19 @@
         <v>308</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>520</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="G213" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="214" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A214" t="s">
         <v>199</v>
       </c>
@@ -8470,19 +8532,19 @@
         <v>308</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>521</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="G214" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="215" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A215" t="s">
         <v>200</v>
       </c>
@@ -8493,19 +8555,19 @@
         <v>308</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>522</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="G215" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.45">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A216" t="s">
         <v>201</v>
       </c>
@@ -8516,19 +8578,19 @@
         <v>308</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>523</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="G216" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="217" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A217" t="s">
         <v>202</v>
       </c>
@@ -8539,19 +8601,19 @@
         <v>308</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>524</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="G217" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="218" spans="1:7" ht="52.5" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:7" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A218" t="s">
         <v>203</v>
       </c>
@@ -8568,13 +8630,13 @@
         <v>525</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="G218" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="219" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A219" t="s">
         <v>204</v>
       </c>
@@ -8585,19 +8647,19 @@
         <v>308</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>526</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G219" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="220" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A220" t="s">
         <v>205</v>
       </c>
@@ -8608,19 +8670,19 @@
         <v>308</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>527</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="G220" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A221" t="s">
         <v>206</v>
       </c>
@@ -8631,19 +8693,19 @@
         <v>308</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>528</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="G221" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="222" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A222" t="s">
         <v>207</v>
       </c>
@@ -8654,19 +8716,19 @@
         <v>308</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>529</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G222" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A223" t="s">
         <v>208</v>
       </c>
@@ -8683,13 +8745,13 @@
         <v>208</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="G223" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A224" t="s">
         <v>209</v>
       </c>
@@ -8706,13 +8768,13 @@
         <v>410</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="G224" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="225" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A225" t="s">
         <v>210</v>
       </c>
@@ -8723,19 +8785,19 @@
         <v>308</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>530</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="G225" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A226" t="s">
         <v>211</v>
       </c>
@@ -8746,19 +8808,19 @@
         <v>308</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>531</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G226" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="227" spans="1:7" ht="78.75" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:7" ht="79.150000000000006" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A227" t="s">
         <v>212</v>
       </c>
@@ -8775,13 +8837,13 @@
         <v>532</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G227" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="228" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A228" t="s">
         <v>213</v>
       </c>
@@ -8792,19 +8854,19 @@
         <v>308</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>533</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="G228" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A229" t="s">
         <v>214</v>
       </c>
@@ -8815,19 +8877,19 @@
         <v>308</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>534</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="G229" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="230" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A230" t="s">
         <v>215</v>
       </c>
@@ -8838,19 +8900,19 @@
         <v>308</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>535</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="G230" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="231" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A231" t="s">
         <v>216</v>
       </c>
@@ -8861,19 +8923,19 @@
         <v>308</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>536</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="G231" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="232" spans="1:7" ht="52.5" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:7" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A232" t="s">
         <v>14</v>
       </c>
@@ -8884,19 +8946,19 @@
         <v>308</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>537</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="G232" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="233" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A233" t="s">
         <v>217</v>
       </c>
@@ -8907,19 +8969,19 @@
         <v>308</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>538</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="G233" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A234" t="s">
         <v>218</v>
       </c>
@@ -8930,19 +8992,19 @@
         <v>308</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>410</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="G234" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="235" spans="1:7" ht="65.650000000000006" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A235" t="s">
         <v>219</v>
       </c>
@@ -8953,19 +9015,19 @@
         <v>308</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>539</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="G235" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.45">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A236" t="s">
         <v>220</v>
       </c>
@@ -8976,19 +9038,19 @@
         <v>308</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>540</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G236" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A237" t="s">
         <v>221</v>
       </c>
@@ -8999,19 +9061,19 @@
         <v>308</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>541</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="G237" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="238" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A238" t="s">
         <v>222</v>
       </c>
@@ -9022,19 +9084,19 @@
         <v>308</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>542</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="G238" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="239" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A239" t="s">
         <v>223</v>
       </c>
@@ -9045,19 +9107,19 @@
         <v>308</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>543</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="G239" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A240" t="s">
         <v>224</v>
       </c>
@@ -9068,19 +9130,19 @@
         <v>308</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>544</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="G240" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="241" spans="1:7" ht="52.5" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:7" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A241" t="s">
         <v>100</v>
       </c>
@@ -9091,19 +9153,19 @@
         <v>308</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>545</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="G241" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A242" t="s">
         <v>214</v>
       </c>
@@ -9114,19 +9176,19 @@
         <v>308</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>534</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G242" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="243" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A243" t="s">
         <v>190</v>
       </c>
@@ -9137,19 +9199,19 @@
         <v>308</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E243" s="2" t="s">
         <v>546</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G243" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.45">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A244" t="s">
         <v>225</v>
       </c>
@@ -9160,19 +9222,19 @@
         <v>308</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E244" s="2" t="s">
         <v>547</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="G244" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="245" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A245" t="s">
         <v>226</v>
       </c>
@@ -9183,19 +9245,19 @@
         <v>308</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E245" s="2" t="s">
         <v>548</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G245" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A246" t="s">
         <v>227</v>
       </c>
@@ -9206,19 +9268,19 @@
         <v>308</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E246" s="2" t="s">
         <v>549</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="G246" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.45">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A247" t="s">
         <v>228</v>
       </c>
@@ -9229,19 +9291,19 @@
         <v>308</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E247" s="2" t="s">
         <v>550</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="G247" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="248" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A248" t="s">
         <v>229</v>
       </c>
@@ -9252,19 +9314,19 @@
         <v>308</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E248" s="2" t="s">
         <v>551</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="G248" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.45">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A249" t="s">
         <v>230</v>
       </c>
@@ -9275,7 +9337,7 @@
         <v>308</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E249" s="2" t="s">
         <v>552</v>
@@ -9284,10 +9346,10 @@
         <v>552</v>
       </c>
       <c r="G249" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A250" t="s">
         <v>31</v>
       </c>
@@ -9298,19 +9360,19 @@
         <v>308</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E250" s="2" t="s">
         <v>553</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="G250" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="251" spans="1:7" ht="52.5" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:7" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A251" t="s">
         <v>231</v>
       </c>
@@ -9321,19 +9383,19 @@
         <v>308</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E251" s="2" t="s">
         <v>554</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="G251" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="252" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A252" t="s">
         <v>232</v>
       </c>
@@ -9344,19 +9406,19 @@
         <v>308</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E252" s="2" t="s">
         <v>555</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="G252" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A253" t="s">
         <v>233</v>
       </c>
@@ -9367,19 +9429,19 @@
         <v>308</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E253" s="2" t="s">
         <v>556</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="G253" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="254" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A254" t="s">
         <v>234</v>
       </c>
@@ -9390,19 +9452,19 @@
         <v>308</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E254" s="2" t="s">
         <v>557</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G254" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="255" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A255" t="s">
         <v>235</v>
       </c>
@@ -9413,19 +9475,19 @@
         <v>308</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E255" s="2" t="s">
         <v>558</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="G255" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A256" t="s">
         <v>156</v>
       </c>
@@ -9436,19 +9498,19 @@
         <v>308</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E256" s="2" t="s">
         <v>559</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="G256" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="257" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A257" t="s">
         <v>236</v>
       </c>
@@ -9459,19 +9521,19 @@
         <v>308</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E257" s="2" t="s">
         <v>560</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="G257" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="258" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A258" t="s">
         <v>237</v>
       </c>
@@ -9482,19 +9544,19 @@
         <v>308</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E258" s="2" t="s">
         <v>561</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="G258" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A259" t="s">
         <v>238</v>
       </c>
@@ -9505,19 +9567,19 @@
         <v>308</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E259" s="2" t="s">
         <v>562</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="G259" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="260" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A260" t="s">
         <v>239</v>
       </c>
@@ -9528,19 +9590,19 @@
         <v>308</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E260" s="2" t="s">
         <v>563</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="G260" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="261" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A261" t="s">
         <v>162</v>
       </c>
@@ -9551,19 +9613,19 @@
         <v>308</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E261" s="2" t="s">
         <v>564</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="G261" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="262" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A262" t="s">
         <v>240</v>
       </c>
@@ -9574,19 +9636,19 @@
         <v>308</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E262" s="2" t="s">
         <v>565</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="G262" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A263" t="s">
         <v>241</v>
       </c>
@@ -9597,19 +9659,19 @@
         <v>308</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E263" s="2" t="s">
         <v>566</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="G263" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.45">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A264" t="s">
         <v>242</v>
       </c>
@@ -9620,19 +9682,19 @@
         <v>308</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E264" s="2" t="s">
         <v>567</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="G264" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A265" t="s">
         <v>243</v>
       </c>
@@ -9643,19 +9705,19 @@
         <v>308</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>568</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="G265" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A266" t="s">
         <v>244</v>
       </c>
@@ -9666,19 +9728,19 @@
         <v>308</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E266" s="2" t="s">
         <v>569</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="G266" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="267" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A267" t="s">
         <v>12</v>
       </c>
@@ -9689,19 +9751,19 @@
         <v>308</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E267" s="2" t="s">
         <v>570</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="G267" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A268" t="s">
         <v>53</v>
       </c>
@@ -9718,13 +9780,13 @@
         <v>410</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G268" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="269" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A269" t="s">
         <v>190</v>
       </c>
@@ -9735,19 +9797,19 @@
         <v>308</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E269" s="2" t="s">
         <v>546</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="G269" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A270" t="s">
         <v>225</v>
       </c>
@@ -9758,19 +9820,19 @@
         <v>308</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E270" s="2" t="s">
         <v>571</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="G270" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.45">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A271" t="s">
         <v>245</v>
       </c>
@@ -9781,19 +9843,19 @@
         <v>308</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E271" s="2" t="s">
         <v>410</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G271" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A272" t="s">
         <v>246</v>
       </c>
@@ -9804,19 +9866,19 @@
         <v>308</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>572</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="G272" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="273" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A273" t="s">
         <v>247</v>
       </c>
@@ -9827,19 +9889,19 @@
         <v>308</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E273" s="2" t="s">
         <v>573</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="G273" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A274" t="s">
         <v>248</v>
       </c>
@@ -9856,13 +9918,13 @@
         <v>410</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G274" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A275" t="s">
         <v>249</v>
       </c>
@@ -9879,13 +9941,13 @@
         <v>410</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G275" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A276" t="s">
         <v>250</v>
       </c>
@@ -9902,13 +9964,13 @@
         <v>510</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="G276" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="277" spans="1:7" ht="52.5" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:7" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A277" t="s">
         <v>66</v>
       </c>
@@ -9919,19 +9981,19 @@
         <v>308</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E277" s="2" t="s">
         <v>574</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="G277" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A278" t="s">
         <v>251</v>
       </c>
@@ -9942,19 +10004,19 @@
         <v>308</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E278" s="2" t="s">
         <v>251</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="G278" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="279" spans="1:7" ht="52.5" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:7" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A279" t="s">
         <v>252</v>
       </c>
@@ -9965,19 +10027,19 @@
         <v>308</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E279" s="2" t="s">
         <v>575</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="G279" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.45">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A280" t="s">
         <v>253</v>
       </c>
@@ -9994,13 +10056,13 @@
         <v>410</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G280" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="281" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A281" t="s">
         <v>30</v>
       </c>
@@ -10011,19 +10073,19 @@
         <v>308</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E281" s="2" t="s">
         <v>576</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="G281" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A282" t="s">
         <v>254</v>
       </c>
@@ -10034,19 +10096,19 @@
         <v>308</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E282" s="2" t="s">
         <v>577</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="G282" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="283" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A283" t="s">
         <v>255</v>
       </c>
@@ -10057,19 +10119,19 @@
         <v>308</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E283" s="2" t="s">
         <v>578</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="G283" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="284" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A284" t="s">
         <v>17</v>
       </c>
@@ -10080,19 +10142,19 @@
         <v>308</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>579</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="G284" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="285" spans="1:7" ht="52.5" x14ac:dyDescent="0.45">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A285" t="s">
         <v>136</v>
       </c>
@@ -10103,19 +10165,19 @@
         <v>308</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E285" s="2" t="s">
         <v>580</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="G285" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="286" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A286" t="s">
         <v>256</v>
       </c>
@@ -10126,19 +10188,19 @@
         <v>308</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E286" s="2" t="s">
         <v>581</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="G286" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="287" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A287" t="s">
         <v>39</v>
       </c>
@@ -10149,19 +10211,19 @@
         <v>308</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E287" s="2" t="s">
         <v>582</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="G287" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="288" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A288" t="s">
         <v>257</v>
       </c>
@@ -10172,19 +10234,19 @@
         <v>308</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E288" s="2" t="s">
         <v>583</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="G288" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="289" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A289" t="s">
         <v>258</v>
       </c>
@@ -10195,19 +10257,19 @@
         <v>309</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E289" s="2" t="s">
         <v>584</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G289" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.45">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A290" t="s">
         <v>49</v>
       </c>
@@ -10224,13 +10286,13 @@
         <v>585</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="G290" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A291" t="s">
         <v>259</v>
       </c>
@@ -10241,19 +10303,19 @@
         <v>309</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E291" s="2" t="s">
         <v>586</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="G291" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A292" t="s">
         <v>260</v>
       </c>
@@ -10264,19 +10326,19 @@
         <v>309</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E292" s="2" t="s">
         <v>587</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="G292" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A293" t="s">
         <v>199</v>
       </c>
@@ -10287,19 +10349,19 @@
         <v>309</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E293" s="2" t="s">
         <v>588</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="G293" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="294" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A294" t="s">
         <v>81</v>
       </c>
@@ -10310,19 +10372,19 @@
         <v>309</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E294" s="2" t="s">
         <v>589</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="G294" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="295" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A295" t="s">
         <v>31</v>
       </c>
@@ -10333,19 +10395,19 @@
         <v>309</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E295" s="2" t="s">
         <v>590</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="G295" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="296" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A296" t="s">
         <v>261</v>
       </c>
@@ -10356,19 +10418,19 @@
         <v>309</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E296" s="2" t="s">
         <v>591</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="G296" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="297" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A297" t="s">
         <v>262</v>
       </c>
@@ -10379,19 +10441,19 @@
         <v>309</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E297" s="2" t="s">
         <v>592</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="G297" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.45">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A298" t="s">
         <v>130</v>
       </c>
@@ -10402,19 +10464,19 @@
         <v>309</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E298" s="2" t="s">
         <v>410</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G298" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="299" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A299" t="s">
         <v>263</v>
       </c>
@@ -10425,19 +10487,19 @@
         <v>309</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E299" s="2" t="s">
         <v>593</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="G299" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="300" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A300" t="s">
         <v>264</v>
       </c>
@@ -10448,19 +10510,19 @@
         <v>309</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E300" s="2" t="s">
         <v>594</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="G300" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="301" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A301" t="s">
         <v>217</v>
       </c>
@@ -10471,19 +10533,19 @@
         <v>309</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E301" s="2" t="s">
         <v>595</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="G301" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="302" spans="1:7" ht="65.650000000000006" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A302" t="s">
         <v>265</v>
       </c>
@@ -10494,19 +10556,19 @@
         <v>309</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E302" s="2" t="s">
         <v>596</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="G302" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A303" t="s">
         <v>266</v>
       </c>
@@ -10517,19 +10579,19 @@
         <v>309</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E303" s="2" t="s">
         <v>410</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G303" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A304" t="s">
         <v>267</v>
       </c>
@@ -10540,19 +10602,19 @@
         <v>309</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E304" s="2" t="s">
         <v>410</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G304" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A305" t="s">
         <v>136</v>
       </c>
@@ -10563,19 +10625,19 @@
         <v>309</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E305" s="2" t="s">
         <v>597</v>
       </c>
       <c r="F305" s="2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="G305" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="306" spans="1:7" ht="52.5" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:7" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A306" t="s">
         <v>268</v>
       </c>
@@ -10586,19 +10648,19 @@
         <v>309</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E306" s="2" t="s">
         <v>598</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="G306" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="307" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A307" t="s">
         <v>269</v>
       </c>
@@ -10609,19 +10671,19 @@
         <v>309</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E307" s="2" t="s">
         <v>599</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="G307" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="308" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A308" t="s">
         <v>64</v>
       </c>
@@ -10632,19 +10694,19 @@
         <v>309</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E308" s="2" t="s">
         <v>600</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="G308" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="309" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A309" t="s">
         <v>270</v>
       </c>
@@ -10655,19 +10717,19 @@
         <v>309</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E309" s="2" t="s">
         <v>601</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G309" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A310" t="s">
         <v>271</v>
       </c>
@@ -10678,19 +10740,19 @@
         <v>309</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E310" s="2" t="s">
         <v>410</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="G310" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A311" t="s">
         <v>214</v>
       </c>
@@ -10701,19 +10763,19 @@
         <v>309</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E311" s="2" t="s">
         <v>602</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="G311" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="312" spans="1:7" ht="52.5" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:7" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A312" t="s">
         <v>272</v>
       </c>
@@ -10724,19 +10786,19 @@
         <v>309</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E312" s="2" t="s">
         <v>603</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="G312" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="313" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A313" t="s">
         <v>273</v>
       </c>
@@ -10753,13 +10815,13 @@
         <v>604</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="G313" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="314" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A314" t="s">
         <v>274</v>
       </c>
@@ -10770,19 +10832,19 @@
         <v>309</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E314" s="2" t="s">
         <v>605</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="G314" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A315" t="s">
         <v>275</v>
       </c>
@@ -10793,19 +10855,19 @@
         <v>309</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E315" s="2" t="s">
         <v>606</v>
       </c>
       <c r="F315" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="G315" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="316" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A316" t="s">
         <v>276</v>
       </c>
@@ -10816,19 +10878,19 @@
         <v>309</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E316" s="2" t="s">
         <v>607</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="G316" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A317" t="s">
         <v>277</v>
       </c>
@@ -10839,19 +10901,19 @@
         <v>309</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E317" s="2" t="s">
         <v>608</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="G317" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="318" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A318" t="s">
         <v>278</v>
       </c>
@@ -10862,19 +10924,19 @@
         <v>309</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E318" s="2" t="s">
         <v>609</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="G318" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="319" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A319" t="s">
         <v>279</v>
       </c>
@@ -10885,19 +10947,19 @@
         <v>309</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E319" s="2" t="s">
         <v>610</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="G319" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A320" t="s">
         <v>16</v>
       </c>
@@ -10908,19 +10970,19 @@
         <v>309</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E320" s="2" t="s">
         <v>611</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="G320" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A321" t="s">
         <v>280</v>
       </c>
@@ -10931,19 +10993,19 @@
         <v>309</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E321" s="2" t="s">
         <v>612</v>
       </c>
       <c r="F321" s="2" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="G321" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A322" t="s">
         <v>281</v>
       </c>
@@ -10954,19 +11016,19 @@
         <v>309</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E322" s="2" t="s">
         <v>410</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G322" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="323" spans="1:7" ht="65.650000000000006" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:7" ht="66" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A323" t="s">
         <v>282</v>
       </c>
@@ -10977,19 +11039,19 @@
         <v>309</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E323" s="2" t="s">
         <v>613</v>
       </c>
       <c r="F323" s="2" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="G323" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="324" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A324" t="s">
         <v>283</v>
       </c>
@@ -11000,19 +11062,19 @@
         <v>309</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E324" s="2" t="s">
         <v>614</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="G324" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="325" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A325" t="s">
         <v>284</v>
       </c>
@@ -11023,19 +11085,19 @@
         <v>309</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E325" s="2" t="s">
         <v>615</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="G325" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A326" t="s">
         <v>285</v>
       </c>
@@ -11046,19 +11108,19 @@
         <v>309</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E326" s="2" t="s">
         <v>616</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="G326" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A327" t="s">
         <v>24</v>
       </c>
@@ -11075,13 +11137,13 @@
         <v>617</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="G327" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="328" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A328" t="s">
         <v>148</v>
       </c>
@@ -11092,19 +11154,19 @@
         <v>309</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E328" s="2" t="s">
         <v>618</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="G328" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="329" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A329" t="s">
         <v>286</v>
       </c>
@@ -11115,19 +11177,19 @@
         <v>309</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E329" s="2" t="s">
         <v>619</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="G329" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A330" t="s">
         <v>287</v>
       </c>
@@ -11138,19 +11200,19 @@
         <v>309</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E330" s="2" t="s">
         <v>620</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="G330" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A331" t="s">
         <v>288</v>
       </c>
@@ -11161,19 +11223,19 @@
         <v>309</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E331" s="2" t="s">
         <v>621</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="G331" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.45">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A332" t="s">
         <v>289</v>
       </c>
@@ -11184,19 +11246,19 @@
         <v>309</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E332" s="2" t="s">
         <v>622</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="G332" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="333" spans="1:7" ht="91.9" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:7" ht="92.25" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A333" t="s">
         <v>290</v>
       </c>
@@ -11207,19 +11269,19 @@
         <v>309</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E333" s="2" t="s">
         <v>623</v>
       </c>
       <c r="F333" s="2" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="G333" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A334" t="s">
         <v>291</v>
       </c>
@@ -11230,19 +11292,19 @@
         <v>309</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E334" s="2" t="s">
         <v>410</v>
       </c>
       <c r="F334" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G334" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="335" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A335" t="s">
         <v>292</v>
       </c>
@@ -11253,19 +11315,19 @@
         <v>309</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E335" s="2" t="s">
         <v>624</v>
       </c>
       <c r="F335" s="2" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="G335" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A336" t="s">
         <v>261</v>
       </c>
@@ -11276,19 +11338,19 @@
         <v>309</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E336" s="2" t="s">
         <v>625</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="G336" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="337" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A337" t="s">
         <v>293</v>
       </c>
@@ -11299,19 +11361,19 @@
         <v>309</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E337" s="2" t="s">
         <v>626</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="G337" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A338" t="s">
         <v>216</v>
       </c>
@@ -11322,7 +11384,7 @@
         <v>309</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E338" s="2" t="s">
         <v>627</v>
@@ -11331,10 +11393,10 @@
         <v>627</v>
       </c>
       <c r="G338" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.45">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A339" t="s">
         <v>40</v>
       </c>
@@ -11345,19 +11407,19 @@
         <v>309</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E339" s="2" t="s">
         <v>628</v>
       </c>
       <c r="F339" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="G339" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="340" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A340" t="s">
         <v>294</v>
       </c>
@@ -11368,19 +11430,19 @@
         <v>309</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E340" s="2" t="s">
         <v>629</v>
       </c>
       <c r="F340" s="2" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="G340" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A341" t="s">
         <v>295</v>
       </c>
@@ -11391,19 +11453,19 @@
         <v>309</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E341" s="2" t="s">
         <v>410</v>
       </c>
       <c r="F341" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G341" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A342" t="s">
         <v>296</v>
       </c>
@@ -11414,19 +11476,19 @@
         <v>309</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E342" s="2" t="s">
         <v>630</v>
       </c>
       <c r="F342" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="G342" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.45">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A343" t="s">
         <v>297</v>
       </c>
@@ -11437,19 +11499,19 @@
         <v>309</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E343" s="2" t="s">
         <v>410</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G343" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="344" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A344" t="s">
         <v>262</v>
       </c>
@@ -11466,13 +11528,13 @@
         <v>631</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="G344" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.45">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A345" t="s">
         <v>298</v>
       </c>
@@ -11489,13 +11551,13 @@
         <v>632</v>
       </c>
       <c r="F345" s="2" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="G345" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A346" t="s">
         <v>299</v>
       </c>
@@ -11512,13 +11574,13 @@
         <v>633</v>
       </c>
       <c r="F346" s="2" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="G346" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="347" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A347" t="s">
         <v>300</v>
       </c>
@@ -11535,13 +11597,13 @@
         <v>634</v>
       </c>
       <c r="F347" s="2" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G347" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="348" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A348" t="s">
         <v>116</v>
       </c>
@@ -11552,19 +11614,19 @@
         <v>309</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E348" s="2" t="s">
         <v>635</v>
       </c>
       <c r="F348" s="2" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="G348" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="349" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A349" t="s">
         <v>35</v>
       </c>
@@ -11575,19 +11637,19 @@
         <v>309</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E349" s="2" t="s">
         <v>636</v>
       </c>
       <c r="F349" s="2" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="G349" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A350" t="s">
         <v>301</v>
       </c>
@@ -11598,19 +11660,19 @@
         <v>309</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E350" s="2" t="s">
         <v>637</v>
       </c>
       <c r="F350" s="2" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="G350" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="351" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A351" t="s">
         <v>31</v>
       </c>
@@ -11621,19 +11683,19 @@
         <v>309</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E351" s="2" t="s">
         <v>638</v>
       </c>
       <c r="F351" s="2" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="G351" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="352" spans="1:7" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:7" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A352" t="s">
         <v>302</v>
       </c>
@@ -11644,19 +11706,19 @@
         <v>309</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E352" s="2" t="s">
         <v>639</v>
       </c>
       <c r="F352" s="2" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="G352" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A353" t="s">
         <v>303</v>
       </c>
@@ -11667,7 +11729,7 @@
         <v>309</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E353" s="2" t="s">
         <v>640</v>
@@ -11679,7 +11741,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="354" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A354" t="s">
         <v>304</v>
       </c>
@@ -11690,19 +11752,19 @@
         <v>309</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E354" s="2" t="s">
         <v>641</v>
       </c>
       <c r="F354" s="2" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="G354" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="355" spans="1:7" ht="39.4" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:7" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A355" t="s">
         <v>305</v>
       </c>
@@ -11713,19 +11775,19 @@
         <v>309</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E355" s="2" t="s">
         <v>642</v>
       </c>
       <c r="F355" s="2" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="G355" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="356" spans="1:7" ht="52.5" x14ac:dyDescent="0.45">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A356" t="s">
         <v>306</v>
       </c>
@@ -11736,19 +11798,19 @@
         <v>309</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E356" s="2" t="s">
-        <v>643</v>
+        <v>995</v>
       </c>
       <c r="F356" s="2" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="G356" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A357" t="s">
         <v>31</v>
       </c>
@@ -11759,26 +11821,1475 @@
         <v>309</v>
       </c>
       <c r="D357" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="E357" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="F357" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="G357" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A359" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A360" t="s">
         <v>987</v>
       </c>
-      <c r="E357" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="F357" s="2" t="s">
-        <v>975</v>
-      </c>
-      <c r="G357" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A359" t="s">
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09911BBF-8C75-448D-8296-ED4E208E7DBB}">
+  <dimension ref="A3:F108"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="3.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.59765625" customWidth="1"/>
+    <col min="3" max="3" width="8.86328125" customWidth="1"/>
+    <col min="4" max="4" width="9.796875" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.53125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:6" ht="28.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A3" s="9" t="s">
+        <v>994</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>993</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>991</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>992</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>990</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>989</v>
       </c>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A360" t="s">
-        <v>988</v>
+    <row r="4" spans="1:6" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="5">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="5">
+        <v>2</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A6" s="5">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A7" s="5">
+        <v>4</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A8" s="5">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="5">
+        <v>6</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A10" s="5">
+        <v>7</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A11" s="5">
+        <v>8</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="5">
+        <v>9</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A13" s="5">
+        <v>10</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="5">
+        <v>11</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A15" s="5">
+        <v>12</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A16" s="5">
+        <v>13</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A17" s="5">
+        <v>14</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A18" s="5">
+        <v>15</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A19" s="5">
+        <v>16</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="66" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A20" s="5">
+        <v>17</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A21" s="5">
+        <v>18</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A22" s="5">
+        <v>19</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A23" s="5">
+        <v>20</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A24" s="5">
+        <v>21</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A25" s="5">
+        <v>22</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="79.150000000000006" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A26" s="5">
+        <v>23</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A27" s="5">
+        <v>24</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="79.150000000000006" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A28" s="5">
+        <v>25</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A29" s="5">
+        <v>26</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A30" s="5">
+        <v>27</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A31" s="5">
+        <v>28</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="79.150000000000006" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A32" s="5">
+        <v>29</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A33" s="5">
+        <v>30</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A34" s="5">
+        <v>31</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A35" s="5">
+        <v>32</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A36" s="5">
+        <v>33</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A37" s="5">
+        <v>34</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A38" s="5">
+        <v>35</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A39" s="5">
+        <v>36</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A40" s="5">
+        <v>37</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A41" s="5">
+        <v>38</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="66" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A42" s="5">
+        <v>39</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A43" s="5">
+        <v>40</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A44" s="5">
+        <v>41</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A45" s="5">
+        <v>42</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="79.150000000000006" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A46" s="5">
+        <v>43</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A47" s="5">
+        <v>44</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="66" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A48" s="5">
+        <v>45</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A49" s="5">
+        <v>46</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A50" s="5">
+        <v>47</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A51" s="5">
+        <v>48</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A52" s="5">
+        <v>49</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A53" s="5">
+        <v>50</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A54" s="5">
+        <v>51</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A55" s="5">
+        <v>52</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A56" s="5">
+        <v>53</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A57" s="5">
+        <v>54</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A58" s="5">
+        <v>55</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A59" s="5">
+        <v>56</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A60" s="5">
+        <v>57</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="92.25" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A61" s="5">
+        <v>58</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="66" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A62" s="5">
+        <v>59</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A63" s="5">
+        <v>60</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A64" s="5">
+        <v>61</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="66" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A65" s="5">
+        <v>62</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A66" s="5">
+        <v>63</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A67" s="5">
+        <v>64</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A68" s="5">
+        <v>65</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A69" s="5">
+        <v>66</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A70" s="5">
+        <v>67</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="66" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A71" s="5">
+        <v>68</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="66" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A72" s="5">
+        <v>69</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A73" s="5">
+        <v>70</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A74" s="5">
+        <v>71</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A75" s="5">
+        <v>72</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A76" s="5">
+        <v>73</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A77" s="5">
+        <v>74</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A78" s="5">
+        <v>75</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="66" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A79" s="5">
+        <v>76</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="66" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A80" s="5">
+        <v>77</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="66" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A81" s="5">
+        <v>78</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A82" s="5">
+        <v>79</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="66" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A83" s="5">
+        <v>80</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A84" s="5">
+        <v>81</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A85" s="5">
+        <v>82</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A86" s="5">
+        <v>83</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A87" s="5">
+        <v>84</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>586</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="66" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A88" s="5">
+        <v>85</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>587</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="66" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A89" s="5">
+        <v>86</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A90" s="5">
+        <v>87</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A91" s="5">
+        <v>88</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A92" s="5">
+        <v>89</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A93" s="5">
+        <v>90</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="26.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A94" s="5">
+        <v>91</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A95" s="5">
+        <v>92</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A96" s="5">
+        <v>93</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A97" s="5">
+        <v>94</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="66" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A98" s="5">
+        <v>95</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A99" s="5">
+        <v>96</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>996</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="66" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A100" s="5">
+        <v>97</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="52.9" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A101" s="5">
+        <v>98</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A102" s="5">
+        <v>99</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="66" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A103" s="5">
+        <v>100</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C105" s="10" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C108" t="s">
+        <v>998</v>
       </c>
     </row>
   </sheetData>
